--- a/input/reg_employment_selection.xlsx
+++ b/input/reg_employment_selection.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="52">
   <si>
     <t>Description:</t>
   </si>
@@ -85,16 +85,10 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Deh_c4_Na</t>
-  </si>
-  <si>
     <t>Deh_c4_Medium</t>
   </si>
   <si>
     <t>Deh_c4_Low</t>
-  </si>
-  <si>
-    <t>Deh_c4_Na_Dag</t>
   </si>
   <si>
     <t>Deh_c4_Medium_Dag</t>
@@ -173,9 +167,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t>Deh_c4_High</t>
   </si>
   <si>
     <t>Dhe_Pcs_L1</t>
@@ -370,7 +361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +467,6 @@
       <c r="AH1" t="s">
         <v>49</v>
       </c>
-      <c r="AI1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -3809,16 +3794,6 @@
       </c>
       <c r="AH33">
         <v>0.016792675240321832</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3850,88 +3825,88 @@
         <v>21</v>
       </c>
       <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>46</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>49</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -4352,7 +4327,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>-0.60046549268497129</v>
@@ -4456,7 +4431,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>-1.3526621233823739</v>
@@ -4560,7 +4535,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.011271653050148329</v>
@@ -4664,7 +4639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>0.022735759260580968</v>
@@ -4768,7 +4743,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>0.070031669130752289</v>
@@ -4872,7 +4847,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>0.074114385954168471</v>
@@ -4976,7 +4951,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>0.092147949897532944</v>
@@ -5080,7 +5055,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>-0.07826874490917006</v>
@@ -5184,7 +5159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>-1.2123552981603063</v>
@@ -5288,7 +5263,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>0.0070339415447928516</v>
@@ -5392,7 +5367,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>0.001347289889830512</v>
@@ -5496,7 +5471,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>-0.13648056657094709</v>
@@ -5600,7 +5575,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>-0.021476611870818351</v>
@@ -5704,7 +5679,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>-0.070683045547237894</v>
@@ -5808,7 +5783,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>0.10164733588695669</v>
@@ -5912,7 +5887,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21">
         <v>0.031617422391000662</v>
@@ -6016,7 +5991,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>0.040535461501967372</v>
@@ -6120,7 +6095,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B23">
         <v>0.058992624931001277</v>
@@ -6224,7 +6199,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24">
         <v>0.079312850513805294</v>
@@ -6328,7 +6303,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>0.019122329213312576</v>
@@ -6432,7 +6407,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>-0.00071557969410492289</v>
@@ -6536,7 +6511,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>-0.018348380964490131</v>
@@ -6640,7 +6615,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B28">
         <v>0.0080001453753408263</v>
@@ -6744,7 +6719,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B29">
         <v>0.058134380819351149</v>
@@ -6848,7 +6823,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>0.051644142496338329</v>
@@ -6952,7 +6927,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>0.1544136975051989</v>
@@ -7056,7 +7031,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>-0.054553465901719646</v>
@@ -7160,7 +7135,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B33">
         <v>-0.68097163290029072</v>
@@ -7268,7 +7243,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH33"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7285,7 +7260,7 @@
         <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>23</v>
@@ -7294,7 +7269,7 @@
         <v>24</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I1" t="s">
         <v>26</v>
@@ -7367,12 +7342,6 @@
       </c>
       <c r="AF1" t="s">
         <v>49</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -7573,7 +7542,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>-0.3455195749500431</v>
@@ -7867,7 +7836,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>0.015580568382061146</v>
@@ -10313,16 +10282,6 @@
       </c>
       <c r="AF31">
         <v>0.010088147152420585</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -10348,88 +10307,88 @@
         <v>21</v>
       </c>
       <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
-        <v>32</v>
-      </c>
       <c r="N1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>38</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>39</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>40</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>41</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>42</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>43</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>45</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>46</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>47</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>48</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>49</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -10630,7 +10589,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>-0.24152853435178601</v>
@@ -10728,7 +10687,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>-0.70484003723359578</v>
@@ -10826,7 +10785,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>0.0078841524904820371</v>
@@ -10924,7 +10883,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>0.015084577379304595</v>
@@ -11022,7 +10981,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0.13770016408471106</v>
@@ -11120,7 +11079,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>0.1390911179167702</v>
@@ -11218,7 +11177,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>0.13258932444671367</v>
@@ -11316,7 +11275,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>0.0049581137544158103</v>
@@ -11414,7 +11373,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>-0.90405110613417816</v>
@@ -11512,7 +11471,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>0.0036309030049698453</v>
@@ -11610,7 +11569,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>0.0061430208070800719</v>
@@ -11708,7 +11667,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>0.035147452292826079</v>
@@ -11806,7 +11765,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>0.12177795111052415</v>
@@ -11904,7 +11863,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>0.12276182668126372</v>
@@ -12002,7 +11961,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>0.14229864556979308</v>
@@ -12100,7 +12059,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>0.066924740536087185</v>
@@ -12198,7 +12157,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>0.1327005328528342</v>
@@ -12296,7 +12255,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>0.08543816771801413</v>
@@ -12394,7 +12353,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>0.18012842074519475</v>
@@ -12492,7 +12451,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>0.091478251530866722</v>
@@ -12590,7 +12549,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>0.10132611654668527</v>
@@ -12688,7 +12647,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25">
         <v>0.1452304327144138</v>
@@ -12786,7 +12745,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>-0.020574446614163806</v>
@@ -12884,7 +12843,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B27">
         <v>-0.029292381294316498</v>
@@ -12982,7 +12941,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>-0.086961525931374684</v>
@@ -13080,7 +13039,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29">
         <v>-0.16541163597606837</v>
@@ -13178,7 +13137,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B30">
         <v>-0.071280114215801424</v>
@@ -13276,7 +13235,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B31">
         <v>-1.5273926557345039</v>
